--- a/artfynd/A 58951-2025 artfynd.xlsx
+++ b/artfynd/A 58951-2025 artfynd.xlsx
@@ -675,49 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3842303</v>
+        <v>74770256</v>
       </c>
       <c r="B2" t="n">
-        <v>103426</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221447</v>
+        <v>219874</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gentianella campestris subsp. campestris</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Morarp (St. Fällan), Sm</t>
+          <t>St. Fällan, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>456132.0272136544</v>
+        <v>456060</v>
       </c>
       <c r="R2" t="n">
-        <v>6371691.510215821</v>
+        <v>6371623</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -739,29 +738,19 @@
           <t>Svenarum</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>F-Vag-0008</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1982-01-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1985-01-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1982-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1985-12-31</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 6E4b 4327. SOM: Platanthera bifolia. LEG: Eva Eriksson</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,30 +770,30 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>F-län Floraväktarna</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eva Eriksson</t>
+          <t>Via Margareta Edqvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74436921</v>
+        <v>3842303</v>
       </c>
       <c r="B3" t="n">
-        <v>105898</v>
+        <v>106414</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -824,17 +813,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>St. Fällan, Sm</t>
+          <t>Morarp (St. Fällan), Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456159</v>
+        <v>456132</v>
       </c>
       <c r="R3" t="n">
-        <v>6371725</v>
+        <v>6371692</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -856,6 +845,11 @@
           <t>Svenarum</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Arkiv-F-Vag-0004</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
           <t>1982-01-01</t>
@@ -864,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>1982-12-31</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 6E4b 4428. SOM: Gentianella campestris. LEG: Eva Eriksson</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,50 +877,46 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>F-län Floraväktarna</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
+          <t>Eva Eriksson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Smålands flora (1978-2007)</t>
+          <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74770256</v>
+        <v>74436921</v>
       </c>
       <c r="B4" t="n">
-        <v>98703</v>
+        <v>106413</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219874</v>
+        <v>221447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fältgentiana</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -939,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456060</v>
+        <v>456159</v>
       </c>
       <c r="R4" t="n">
-        <v>6371623</v>
+        <v>6371725</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -969,17 +954,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1985-01-01</t>
+          <t>1982-01-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1985-12-31</t>
+          <t>1982-12-31</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6E4b 4327. SOM: Platanthera bifolia. LEG: Eva Eriksson</t>
+          <t>Smålands flora 2007: KOO: 6E4b 4428. SOM: Gentianella campestris. LEG: Eva Eriksson</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 58951-2025 artfynd.xlsx
+++ b/artfynd/A 58951-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74770256</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3842303</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,8 +1012,18 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74436921</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>